--- a/268/food/2026-02-06-sm.xlsx
+++ b/268/food/2026-02-06-sm.xlsx
@@ -3,13 +3,13 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="11400" windowHeight="5895" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Лист_1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1" refMode="R1C1"/>
 </workbook>
 </file>
 
@@ -18,17 +18,30 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Arial"/>
       <sz val="8"/>
     </font>
     <font>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <family val="2"/>
+      <strike val="0"/>
+      <sz val="8"/>
+    </font>
+    <font>
       <name val="Calibri"/>
+      <charset val="0"/>
+      <family val="0"/>
+      <strike val="0"/>
       <sz val="11"/>
     </font>
     <font>
       <name val="Calibri"/>
+      <charset val="0"/>
+      <family val="0"/>
+      <strike val="0"/>
       <sz val="1"/>
     </font>
   </fonts>
@@ -41,7 +54,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFF2CB"/>
+        <fgColor rgb="00FFF2CB"/>
         <bgColor auto="1"/>
       </patternFill>
     </fill>
@@ -57,13 +70,13 @@
     <border>
       <left/>
       <right style="thin">
-        <color rgb="FF000000"/>
+        <color rgb="00000000"/>
       </right>
       <top style="thin">
-        <color rgb="FF000000"/>
+        <color rgb="00000000"/>
       </top>
       <bottom style="thin">
-        <color rgb="FF000000"/>
+        <color rgb="00000000"/>
       </bottom>
       <diagonal/>
     </border>
@@ -71,38 +84,38 @@
       <left/>
       <right/>
       <top style="thin">
-        <color rgb="FF000000"/>
+        <color rgb="00000000"/>
       </top>
       <bottom style="thin">
-        <color rgb="FF000000"/>
+        <color rgb="00000000"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF000000"/>
+        <color rgb="00000000"/>
       </left>
       <right/>
       <top style="thin">
-        <color rgb="FF000000"/>
+        <color rgb="00000000"/>
       </top>
       <bottom style="thin">
-        <color rgb="FF000000"/>
+        <color rgb="00000000"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF000000"/>
+        <color rgb="00000000"/>
       </left>
       <right style="thin">
-        <color rgb="FF000000"/>
+        <color rgb="00000000"/>
       </right>
       <top style="thin">
-        <color rgb="FF000000"/>
+        <color rgb="00000000"/>
       </top>
       <bottom style="thin">
-        <color rgb="FF000000"/>
+        <color rgb="00000000"/>
       </bottom>
       <diagonal/>
     </border>
@@ -111,37 +124,37 @@
       <right/>
       <top/>
       <bottom style="thin">
-        <color rgb="FF000000"/>
+        <color rgb="00000000"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="medium">
-        <color rgb="FF000000"/>
+        <color rgb="00000000"/>
       </left>
       <right style="thin">
-        <color rgb="FF000000"/>
+        <color rgb="00000000"/>
       </right>
       <top style="medium">
-        <color rgb="FF000000"/>
+        <color rgb="00000000"/>
       </top>
       <bottom style="medium">
-        <color rgb="FF000000"/>
+        <color rgb="00000000"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF000000"/>
+        <color rgb="00000000"/>
       </left>
       <right style="thin">
-        <color rgb="FF000000"/>
+        <color rgb="00000000"/>
       </right>
       <top style="medium">
-        <color rgb="FF000000"/>
+        <color rgb="00000000"/>
       </top>
       <bottom style="medium">
-        <color rgb="FF000000"/>
+        <color rgb="00000000"/>
       </bottom>
       <diagonal/>
     </border>
@@ -149,75 +162,77 @@
       <left/>
       <right/>
       <top style="medium">
-        <color rgb="FF000000"/>
+        <color rgb="00000000"/>
       </top>
       <bottom style="medium">
-        <color rgb="FF000000"/>
+        <color rgb="00000000"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left/>
       <right style="medium">
-        <color rgb="FF000000"/>
+        <color rgb="00000000"/>
       </right>
       <top style="medium">
-        <color rgb="FF000000"/>
+        <color rgb="00000000"/>
       </top>
       <bottom style="medium">
-        <color rgb="FF000000"/>
+        <color rgb="00000000"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="medium">
-        <color rgb="FF000000"/>
+        <color rgb="00000000"/>
       </left>
       <right style="thin">
-        <color rgb="FF000000"/>
+        <color rgb="00000000"/>
       </right>
       <top style="medium">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom/>
+        <color rgb="00000000"/>
+      </top>
+      <bottom>
+        <color rgb="00000000"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF000000"/>
+        <color rgb="00000000"/>
       </left>
       <right style="thin">
-        <color rgb="FF000000"/>
+        <color rgb="00000000"/>
       </right>
       <top style="medium">
-        <color rgb="FF000000"/>
+        <color rgb="00000000"/>
       </top>
       <bottom style="thin">
-        <color rgb="FF000000"/>
+        <color rgb="00000000"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF000000"/>
+        <color rgb="00000000"/>
       </left>
       <right style="medium">
-        <color rgb="FF000000"/>
+        <color rgb="00000000"/>
       </right>
       <top style="medium">
-        <color rgb="FF000000"/>
+        <color rgb="00000000"/>
       </top>
       <bottom style="thin">
-        <color rgb="FF000000"/>
+        <color rgb="00000000"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="medium">
-        <color rgb="FF000000"/>
+        <color rgb="00000000"/>
       </left>
       <right style="thin">
-        <color rgb="FF000000"/>
+        <color rgb="00000000"/>
       </right>
       <top/>
       <bottom/>
@@ -225,59 +240,59 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF000000"/>
+        <color rgb="00000000"/>
       </left>
       <right style="medium">
-        <color rgb="FF000000"/>
+        <color rgb="00000000"/>
       </right>
       <top style="thin">
-        <color rgb="FF000000"/>
+        <color rgb="00000000"/>
       </top>
       <bottom style="thin">
-        <color rgb="FF000000"/>
+        <color rgb="00000000"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="medium">
-        <color rgb="FF000000"/>
+        <color rgb="00000000"/>
       </left>
       <right style="thin">
-        <color rgb="FF000000"/>
+        <color rgb="00000000"/>
       </right>
       <top/>
       <bottom style="medium">
-        <color rgb="FF000000"/>
+        <color rgb="00000000"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF000000"/>
+        <color rgb="00000000"/>
       </left>
       <right style="thin">
-        <color rgb="FF000000"/>
+        <color rgb="00000000"/>
       </right>
       <top style="thin">
-        <color rgb="FF000000"/>
+        <color rgb="00000000"/>
       </top>
       <bottom style="medium">
-        <color rgb="FF000000"/>
+        <color rgb="00000000"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF000000"/>
+        <color rgb="00000000"/>
       </left>
       <right style="medium">
-        <color rgb="FF000000"/>
+        <color rgb="00000000"/>
       </right>
       <top style="thin">
-        <color rgb="FF000000"/>
+        <color rgb="00000000"/>
       </top>
       <bottom style="medium">
-        <color rgb="FF000000"/>
+        <color rgb="00000000"/>
       </bottom>
       <diagonal/>
     </border>
@@ -285,7 +300,7 @@
       <left/>
       <right/>
       <top style="thin">
-        <color rgb="FF000000"/>
+        <color rgb="00000000"/>
       </top>
       <bottom/>
       <diagonal/>
@@ -293,10 +308,10 @@
     <border>
       <left/>
       <right style="thin">
-        <color rgb="FF000000"/>
+        <color rgb="00000000"/>
       </right>
       <top style="thin">
-        <color rgb="FF000000"/>
+        <color rgb="00000000"/>
       </top>
       <bottom/>
       <diagonal/>
@@ -305,115 +320,139 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="centerContinuous" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="centerContinuous" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="centerContinuous" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="1" fontId="1" fillId="2" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="2" fontId="1" fillId="2" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="1" fontId="2" fillId="2" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="2" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="2" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="2" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="1" fontId="1" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="2" fontId="1" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="1" fontId="2" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="2" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="2" fillId="2" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="2" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="2" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -491,9 +530,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -531,7 +570,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -565,7 +604,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -600,10 +638,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -779,20 +816,20 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
-    <pageSetUpPr autoPageBreaks="0"/>
+    <pageSetUpPr autoPageBreaks="0" fitToPage="0"/>
   </sheetPr>
   <dimension ref="A1:J19"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="10.5" defaultRowHeight="11.45" customHeight="1"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="10.5" defaultRowHeight="11.429" customHeight="1"/>
   <cols>
     <col width="16.83203125" customWidth="1" style="1" min="1" max="1"/>
-    <col width="15.6640625" customWidth="1" style="1" min="2" max="2"/>
+    <col width="15.66796875" customWidth="1" style="1" min="2" max="2"/>
     <col width="14.33203125" customWidth="1" style="1" min="3" max="3"/>
     <col width="59.5" customWidth="1" style="1" min="4" max="4"/>
     <col width="11.83203125" customWidth="1" style="1" min="5" max="5"/>
     <col width="12.5" customWidth="1" style="1" min="6" max="6"/>
     <col width="16.5" customWidth="1" style="1" min="7" max="7"/>
     <col width="10.83203125" customWidth="1" style="1" min="8" max="8"/>
-    <col width="11.1640625" customWidth="1" style="1" min="9" max="9"/>
+    <col width="11.16796875" customWidth="1" style="1" min="9" max="9"/>
     <col width="12.33203125" customWidth="1" style="1" min="10" max="10"/>
   </cols>
   <sheetData>
@@ -802,521 +839,529 @@
           <t>Школа</t>
         </is>
       </c>
-      <c r="B1" s="3" t="inlineStr">
+      <c r="B1" s="9" t="inlineStr">
         <is>
           <t>МБОУ «СОШ №4 г.Шали»</t>
         </is>
       </c>
-      <c r="C1" s="36" t="n"/>
-      <c r="D1" s="37" t="n"/>
+      <c r="C1" s="40" t="n"/>
+      <c r="D1" s="41" t="n"/>
       <c r="E1" s="2" t="inlineStr">
         <is>
           <t>Отд./корп</t>
         </is>
       </c>
-      <c r="F1" s="3" t="n"/>
-      <c r="G1" s="4" t="n"/>
+      <c r="F1" s="9" t="e"/>
+      <c r="G1" s="10" t="e"/>
       <c r="I1" s="2" t="inlineStr">
         <is>
           <t>День</t>
         </is>
       </c>
-      <c r="J1" s="35" t="inlineStr">
+      <c r="J1" s="11" t="inlineStr">
         <is>
           <t>2026-02-06</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="3.95" customFormat="1" customHeight="1" s="1">
-      <c r="B2" s="5" t="n"/>
-      <c r="C2" s="5" t="n"/>
-      <c r="D2" s="5" t="n"/>
+    <row r="2" ht="4" customFormat="1" customHeight="1" s="1">
+      <c r="B2" s="12" t="e"/>
+      <c r="C2" s="12" t="e"/>
+      <c r="D2" s="12" t="e"/>
     </row>
     <row r="3" ht="15" customHeight="1">
-      <c r="A3" s="6" t="inlineStr">
+      <c r="A3" s="13" t="inlineStr">
         <is>
           <t>Прием пищи</t>
         </is>
       </c>
-      <c r="B3" s="7" t="inlineStr">
+      <c r="B3" s="14" t="inlineStr">
         <is>
           <t>Раздел</t>
         </is>
       </c>
-      <c r="C3" s="7" t="inlineStr">
+      <c r="C3" s="14" t="inlineStr">
         <is>
           <t>№ рец.</t>
         </is>
       </c>
-      <c r="D3" s="8" t="inlineStr">
+      <c r="D3" s="15" t="inlineStr">
         <is>
           <t>Блюдо</t>
         </is>
       </c>
-      <c r="E3" s="7" t="inlineStr">
+      <c r="E3" s="14" t="inlineStr">
         <is>
           <t>Выход, г</t>
         </is>
       </c>
-      <c r="F3" s="8" t="inlineStr">
+      <c r="F3" s="15" t="inlineStr">
         <is>
           <t>Цена</t>
         </is>
       </c>
-      <c r="G3" s="7" t="inlineStr">
+      <c r="G3" s="14" t="inlineStr">
         <is>
           <t>Калорийность</t>
         </is>
       </c>
-      <c r="H3" s="8" t="inlineStr">
+      <c r="H3" s="15" t="inlineStr">
         <is>
           <t>Белки</t>
         </is>
       </c>
-      <c r="I3" s="7" t="inlineStr">
+      <c r="I3" s="14" t="inlineStr">
         <is>
           <t>Жиры</t>
         </is>
       </c>
-      <c r="J3" s="9" t="inlineStr">
+      <c r="J3" s="16" t="inlineStr">
         <is>
           <t>Углеводы</t>
         </is>
       </c>
     </row>
     <row r="4" ht="15" customHeight="1">
-      <c r="A4" s="10" t="inlineStr">
+      <c r="A4" s="17" t="inlineStr">
         <is>
           <t>Завтрак</t>
         </is>
       </c>
-      <c r="B4" s="11" t="inlineStr">
+      <c r="B4" s="20" t="inlineStr">
         <is>
           <t>гор.блюдо</t>
         </is>
       </c>
-      <c r="C4" s="12" t="n"/>
-      <c r="D4" s="11" t="inlineStr">
+      <c r="C4" s="19" t="e"/>
+      <c r="D4" s="20" t="inlineStr">
         <is>
           <t>Котлета куриная</t>
         </is>
       </c>
-      <c r="E4" s="13" t="n">
+      <c r="E4" s="21" t="n">
         <v>70</v>
       </c>
-      <c r="F4" s="14" t="n">
+      <c r="F4" s="22" t="n">
         <v>18.35</v>
       </c>
-      <c r="G4" s="13" t="n">
+      <c r="G4" s="21" t="n">
         <v>218</v>
       </c>
-      <c r="H4" s="15" t="n">
+      <c r="H4" s="42" t="n">
         <v>6.7</v>
       </c>
-      <c r="I4" s="15" t="n">
+      <c r="I4" s="42" t="n">
         <v>12.6</v>
       </c>
-      <c r="J4" s="16" t="n">
+      <c r="J4" s="43" t="n">
         <v>19.6</v>
       </c>
     </row>
     <row r="5" ht="15" customHeight="1">
-      <c r="A5" s="17" t="n"/>
-      <c r="B5" s="18" t="inlineStr">
+      <c r="A5" s="25" t="e"/>
+      <c r="B5" s="26" t="inlineStr">
         <is>
           <t>гор.блюдо</t>
         </is>
       </c>
-      <c r="C5" s="19" t="inlineStr">
+      <c r="C5" s="27" t="inlineStr">
         <is>
           <t>304</t>
         </is>
       </c>
-      <c r="D5" s="18" t="inlineStr">
+      <c r="D5" s="26" t="inlineStr">
         <is>
           <t>Рис отварной №304</t>
         </is>
       </c>
-      <c r="E5" s="20" t="n">
+      <c r="E5" s="28" t="n">
         <v>100</v>
       </c>
-      <c r="F5" s="21" t="n">
+      <c r="F5" s="29" t="n">
         <v>12.85</v>
       </c>
-      <c r="G5" s="20" t="n">
+      <c r="G5" s="28" t="n">
         <v>130</v>
       </c>
-      <c r="H5" s="22" t="n">
+      <c r="H5" s="44" t="n">
         <v>2.4</v>
       </c>
-      <c r="I5" s="22" t="n">
+      <c r="I5" s="44" t="n">
         <v>3.6</v>
       </c>
-      <c r="J5" s="23" t="n">
+      <c r="J5" s="45" t="n">
         <v>24.5</v>
       </c>
     </row>
     <row r="6" ht="15" customHeight="1">
-      <c r="A6" s="17" t="n"/>
-      <c r="B6" s="18" t="inlineStr">
+      <c r="A6" s="25" t="e"/>
+      <c r="B6" s="26" t="inlineStr">
         <is>
           <t>гор.напиток</t>
         </is>
       </c>
-      <c r="C6" s="19" t="inlineStr">
+      <c r="C6" s="27" t="inlineStr">
         <is>
           <t>459</t>
         </is>
       </c>
-      <c r="D6" s="18" t="inlineStr">
+      <c r="D6" s="26" t="inlineStr">
         <is>
           <t>Чай с лимоном №459</t>
         </is>
       </c>
-      <c r="E6" s="20" t="n">
+      <c r="E6" s="28" t="n">
         <v>180</v>
       </c>
-      <c r="F6" s="21" t="n">
+      <c r="F6" s="29" t="n">
         <v>33.04</v>
       </c>
-      <c r="G6" s="20" t="n">
+      <c r="G6" s="28" t="n">
         <v>35</v>
       </c>
-      <c r="H6" s="24" t="n"/>
-      <c r="I6" s="22" t="n">
+      <c r="H6" s="32" t="e"/>
+      <c r="I6" s="44" t="n">
         <v>0.1</v>
       </c>
-      <c r="J6" s="23" t="n">
+      <c r="J6" s="45" t="n">
         <v>8.6</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
-      <c r="A7" s="17" t="n"/>
-      <c r="B7" s="18" t="inlineStr">
+      <c r="A7" s="25" t="e"/>
+      <c r="B7" s="26" t="inlineStr">
         <is>
           <t>хлеб</t>
         </is>
       </c>
-      <c r="C7" s="19" t="n"/>
-      <c r="D7" s="18" t="inlineStr">
+      <c r="C7" s="27" t="e"/>
+      <c r="D7" s="26" t="inlineStr">
         <is>
           <t>Хлеб пшеничный</t>
         </is>
       </c>
-      <c r="E7" s="20" t="n">
+      <c r="E7" s="28" t="n">
         <v>50</v>
       </c>
-      <c r="F7" s="21" t="n">
+      <c r="F7" s="29" t="n">
         <v>9.18</v>
       </c>
-      <c r="G7" s="20" t="n">
+      <c r="G7" s="28" t="n">
         <v>121</v>
       </c>
-      <c r="H7" s="22" t="n">
+      <c r="H7" s="44" t="n">
         <v>3.9</v>
       </c>
-      <c r="I7" s="22" t="n">
+      <c r="I7" s="44" t="n">
         <v>0.5</v>
       </c>
-      <c r="J7" s="23" t="n">
+      <c r="J7" s="45" t="n">
         <v>24.1</v>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1">
-      <c r="A8" s="17" t="n"/>
-      <c r="B8" s="18" t="inlineStr">
+      <c r="A8" s="25" t="e"/>
+      <c r="B8" s="26" t="inlineStr">
         <is>
           <t>фрукты</t>
         </is>
       </c>
-      <c r="C8" s="19" t="inlineStr">
+      <c r="C8" s="27" t="inlineStr">
         <is>
           <t>338</t>
         </is>
       </c>
-      <c r="D8" s="18" t="inlineStr">
+      <c r="D8" s="26" t="inlineStr">
         <is>
           <t>Яблоко №338</t>
         </is>
       </c>
-      <c r="E8" s="20" t="n">
+      <c r="E8" s="28" t="n">
         <v>100</v>
       </c>
-      <c r="F8" s="21" t="n">
+      <c r="F8" s="29" t="n">
         <v>18.35</v>
       </c>
-      <c r="G8" s="20" t="n">
+      <c r="G8" s="28" t="n">
         <v>76</v>
       </c>
-      <c r="H8" s="22" t="n">
+      <c r="H8" s="44" t="n">
         <v>1.2</v>
       </c>
-      <c r="I8" s="22" t="n">
+      <c r="I8" s="44" t="n">
         <v>0.4</v>
       </c>
-      <c r="J8" s="23" t="n">
+      <c r="J8" s="45" t="n">
         <v>16.8</v>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1">
-      <c r="A9" s="17" t="n"/>
-      <c r="B9" s="18" t="n"/>
-      <c r="C9" s="19" t="n"/>
-      <c r="D9" s="18" t="n"/>
-      <c r="E9" s="24" t="n"/>
-      <c r="F9" s="24" t="n"/>
-      <c r="G9" s="24" t="n"/>
-      <c r="H9" s="24" t="n"/>
-      <c r="I9" s="24" t="n"/>
-      <c r="J9" s="25" t="n"/>
+      <c r="A9" s="25" t="e"/>
+      <c r="B9" s="26" t="e"/>
+      <c r="C9" s="27" t="e"/>
+      <c r="D9" s="26" t="e"/>
+      <c r="E9" s="32" t="e"/>
+      <c r="F9" s="32" t="e"/>
+      <c r="G9" s="32" t="e"/>
+      <c r="H9" s="32" t="e"/>
+      <c r="I9" s="32" t="e"/>
+      <c r="J9" s="33" t="e"/>
     </row>
     <row r="10" ht="15" customHeight="1">
-      <c r="A10" s="17" t="n"/>
-      <c r="B10" s="18" t="n"/>
-      <c r="C10" s="19" t="n"/>
-      <c r="D10" s="18" t="n"/>
-      <c r="E10" s="24" t="n"/>
-      <c r="F10" s="24" t="n"/>
-      <c r="G10" s="24" t="n"/>
-      <c r="H10" s="24" t="n"/>
-      <c r="I10" s="24" t="n"/>
-      <c r="J10" s="25" t="n"/>
+      <c r="A10" s="25" t="e"/>
+      <c r="B10" s="26" t="e"/>
+      <c r="C10" s="27" t="e"/>
+      <c r="D10" s="26" t="e"/>
+      <c r="E10" s="32" t="e"/>
+      <c r="F10" s="32" t="e"/>
+      <c r="G10" s="32" t="e"/>
+      <c r="H10" s="32" t="e"/>
+      <c r="I10" s="32" t="e"/>
+      <c r="J10" s="33" t="e"/>
     </row>
     <row r="11" ht="15" customHeight="1">
-      <c r="A11" s="10" t="inlineStr">
+      <c r="A11" s="17" t="inlineStr">
         <is>
           <t>Обед</t>
         </is>
       </c>
-      <c r="B11" s="11" t="inlineStr">
+      <c r="B11" s="20" t="inlineStr">
         <is>
           <t>закуска</t>
         </is>
       </c>
-      <c r="C11" s="12" t="n"/>
-      <c r="D11" s="11" t="n"/>
-      <c r="E11" s="26" t="n"/>
-      <c r="F11" s="26" t="n"/>
-      <c r="G11" s="26" t="n"/>
-      <c r="H11" s="26" t="n"/>
-      <c r="I11" s="26" t="n"/>
-      <c r="J11" s="27" t="n"/>
+      <c r="C11" s="19" t="e"/>
+      <c r="D11" s="20" t="e"/>
+      <c r="E11" s="34" t="e"/>
+      <c r="F11" s="34" t="e"/>
+      <c r="G11" s="34" t="e"/>
+      <c r="H11" s="34" t="e"/>
+      <c r="I11" s="34" t="e"/>
+      <c r="J11" s="35" t="e"/>
     </row>
     <row r="12" ht="15" customHeight="1">
-      <c r="A12" s="17" t="n"/>
-      <c r="B12" s="18" t="inlineStr">
+      <c r="A12" s="25" t="e"/>
+      <c r="B12" s="26" t="inlineStr">
         <is>
           <t>1 блюдо</t>
         </is>
       </c>
-      <c r="C12" s="19" t="inlineStr">
+      <c r="C12" s="27" t="inlineStr">
         <is>
           <t>127</t>
         </is>
       </c>
-      <c r="D12" s="18" t="inlineStr">
+      <c r="D12" s="26" t="inlineStr">
         <is>
           <t>Суп гороховый №127</t>
         </is>
       </c>
-      <c r="E12" s="20" t="n">
+      <c r="E12" s="28" t="n">
         <v>200</v>
       </c>
-      <c r="F12" s="21" t="n">
+      <c r="F12" s="29" t="n">
         <v>18.35</v>
       </c>
-      <c r="G12" s="20" t="n">
+      <c r="G12" s="28" t="n">
         <v>98</v>
       </c>
-      <c r="H12" s="22" t="n">
+      <c r="H12" s="44" t="n">
         <v>5.9</v>
       </c>
-      <c r="I12" s="22" t="n">
+      <c r="I12" s="44" t="n">
         <v>2.6</v>
       </c>
-      <c r="J12" s="23" t="n">
+      <c r="J12" s="45" t="n">
         <v>12.6</v>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1">
-      <c r="A13" s="17" t="n"/>
-      <c r="B13" s="18" t="inlineStr">
+      <c r="A13" s="25" t="e"/>
+      <c r="B13" s="26" t="inlineStr">
         <is>
           <t>2 блюдо</t>
         </is>
       </c>
-      <c r="C13" s="19" t="n"/>
-      <c r="D13" s="18" t="inlineStr">
+      <c r="C13" s="27" t="e"/>
+      <c r="D13" s="26" t="inlineStr">
         <is>
           <t>Котлета куриная</t>
         </is>
       </c>
-      <c r="E13" s="20" t="n">
+      <c r="E13" s="28" t="n">
         <v>90</v>
       </c>
-      <c r="F13" s="21" t="n">
+      <c r="F13" s="29" t="n">
         <v>23.25</v>
       </c>
-      <c r="G13" s="20" t="n">
+      <c r="G13" s="28" t="n">
         <v>282</v>
       </c>
-      <c r="H13" s="22" t="n">
+      <c r="H13" s="44" t="n">
         <v>8.6</v>
       </c>
-      <c r="I13" s="22" t="n">
+      <c r="I13" s="44" t="n">
         <v>16.3</v>
       </c>
-      <c r="J13" s="23" t="n">
+      <c r="J13" s="45" t="n">
         <v>25.3</v>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
-      <c r="A14" s="17" t="n"/>
-      <c r="B14" s="18" t="inlineStr">
+      <c r="A14" s="25" t="e"/>
+      <c r="B14" s="26" t="inlineStr">
         <is>
           <t>гарнир</t>
         </is>
       </c>
-      <c r="C14" s="19" t="inlineStr">
+      <c r="C14" s="27" t="inlineStr">
         <is>
           <t>304</t>
         </is>
       </c>
-      <c r="D14" s="18" t="inlineStr">
+      <c r="D14" s="26" t="inlineStr">
         <is>
           <t>Рис отварной №304</t>
         </is>
       </c>
-      <c r="E14" s="20" t="n">
+      <c r="E14" s="28" t="n">
         <v>150</v>
       </c>
-      <c r="F14" s="21" t="n">
+      <c r="F14" s="29" t="n">
         <v>18.35</v>
       </c>
-      <c r="G14" s="20" t="n">
+      <c r="G14" s="28" t="n">
         <v>210</v>
       </c>
-      <c r="H14" s="22" t="n">
+      <c r="H14" s="44" t="n">
         <v>3.6</v>
       </c>
-      <c r="I14" s="22" t="n">
+      <c r="I14" s="44" t="n">
         <v>5.4</v>
       </c>
-      <c r="J14" s="23" t="n">
+      <c r="J14" s="45" t="n">
         <v>36.7</v>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
-      <c r="A15" s="17" t="n"/>
-      <c r="B15" s="18" t="inlineStr">
+      <c r="A15" s="25" t="e"/>
+      <c r="B15" s="26" t="inlineStr">
         <is>
           <t>напиток</t>
         </is>
       </c>
-      <c r="C15" s="19" t="inlineStr">
+      <c r="C15" s="27" t="inlineStr">
         <is>
           <t>459</t>
         </is>
       </c>
-      <c r="D15" s="18" t="inlineStr">
+      <c r="D15" s="26" t="inlineStr">
         <is>
           <t>Чай с лимоном №459</t>
         </is>
       </c>
-      <c r="E15" s="20" t="n">
+      <c r="E15" s="28" t="n">
         <v>180</v>
       </c>
-      <c r="F15" s="21" t="n">
+      <c r="F15" s="29" t="n">
         <v>4.09</v>
       </c>
-      <c r="G15" s="20" t="n">
+      <c r="G15" s="28" t="n">
         <v>35</v>
       </c>
-      <c r="H15" s="24" t="n"/>
-      <c r="I15" s="22" t="n">
+      <c r="H15" s="32" t="e"/>
+      <c r="I15" s="44" t="n">
         <v>0.1</v>
       </c>
-      <c r="J15" s="23" t="n">
+      <c r="J15" s="45" t="n">
         <v>8.6</v>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
-      <c r="A16" s="17" t="n"/>
-      <c r="B16" s="18" t="inlineStr">
+      <c r="A16" s="25" t="e"/>
+      <c r="B16" s="26" t="inlineStr">
         <is>
           <t>хлеб бел.</t>
         </is>
       </c>
-      <c r="C16" s="19" t="n"/>
-      <c r="D16" s="18" t="inlineStr">
+      <c r="C16" s="27" t="e"/>
+      <c r="D16" s="26" t="inlineStr">
         <is>
           <t>Хлеб пшеничный</t>
         </is>
       </c>
-      <c r="E16" s="20" t="n">
+      <c r="E16" s="28" t="n">
         <v>80</v>
       </c>
-      <c r="F16" s="21" t="n">
+      <c r="F16" s="29" t="n">
         <v>27.73</v>
       </c>
-      <c r="G16" s="20" t="n">
+      <c r="G16" s="28" t="n">
         <v>187</v>
       </c>
-      <c r="H16" s="22" t="n">
+      <c r="H16" s="44" t="n">
         <v>6.3</v>
       </c>
-      <c r="I16" s="22" t="n">
+      <c r="I16" s="44" t="n">
         <v>0.8</v>
       </c>
-      <c r="J16" s="23" t="n">
+      <c r="J16" s="45" t="n">
         <v>38.6</v>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
-      <c r="A17" s="17" t="n"/>
-      <c r="B17" s="18" t="inlineStr">
+      <c r="A17" s="25" t="e"/>
+      <c r="B17" s="26" t="inlineStr">
         <is>
           <t>хлеб черн.</t>
         </is>
       </c>
-      <c r="C17" s="19" t="n"/>
-      <c r="D17" s="18" t="n"/>
-      <c r="E17" s="24" t="n"/>
-      <c r="F17" s="24" t="n"/>
-      <c r="G17" s="24" t="n"/>
-      <c r="H17" s="24" t="n"/>
-      <c r="I17" s="24" t="n"/>
-      <c r="J17" s="25" t="n"/>
+      <c r="C17" s="27" t="e"/>
+      <c r="D17" s="26" t="e"/>
+      <c r="E17" s="32" t="e"/>
+      <c r="F17" s="32" t="e"/>
+      <c r="G17" s="32" t="e"/>
+      <c r="H17" s="32" t="e"/>
+      <c r="I17" s="32" t="e"/>
+      <c r="J17" s="33" t="e"/>
     </row>
     <row r="18" ht="15" customHeight="1">
-      <c r="A18" s="17" t="n"/>
-      <c r="B18" s="18" t="n"/>
-      <c r="C18" s="19" t="n"/>
-      <c r="D18" s="18" t="n"/>
-      <c r="E18" s="24" t="n"/>
-      <c r="F18" s="24" t="n"/>
-      <c r="G18" s="24" t="n"/>
-      <c r="H18" s="24" t="n"/>
-      <c r="I18" s="24" t="n"/>
-      <c r="J18" s="25" t="n"/>
+      <c r="A18" s="25" t="e"/>
+      <c r="B18" s="26" t="e"/>
+      <c r="C18" s="27" t="e"/>
+      <c r="D18" s="26" t="e"/>
+      <c r="E18" s="32" t="e"/>
+      <c r="F18" s="32" t="e"/>
+      <c r="G18" s="32" t="e"/>
+      <c r="H18" s="32" t="e"/>
+      <c r="I18" s="32" t="e"/>
+      <c r="J18" s="33" t="e"/>
     </row>
     <row r="19" ht="15" customHeight="1">
-      <c r="A19" s="28" t="n"/>
-      <c r="B19" s="29" t="n"/>
-      <c r="C19" s="30" t="n"/>
-      <c r="D19" s="29" t="n"/>
-      <c r="E19" s="30" t="n"/>
-      <c r="F19" s="30" t="n"/>
-      <c r="G19" s="30" t="n"/>
-      <c r="H19" s="30" t="n"/>
-      <c r="I19" s="30" t="n"/>
-      <c r="J19" s="31" t="n"/>
+      <c r="A19" s="36" t="e"/>
+      <c r="B19" s="37" t="e"/>
+      <c r="C19" s="38" t="e"/>
+      <c r="D19" s="37" t="e"/>
+      <c r="E19" s="38" t="e"/>
+      <c r="F19" s="38" t="e"/>
+      <c r="G19" s="38" t="e"/>
+      <c r="H19" s="38" t="e"/>
+      <c r="I19" s="38" t="e"/>
+      <c r="J19" s="39" t="e"/>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="B1:D1"/>
   </mergeCells>
   <pageMargins left="0.3937007874015748" right="0.3937007874015748" top="0.3937007874015748" bottom="0.3937007874015748" header="0" footer="0"/>
-  <pageSetup orientation="portrait" pageOrder="overThenDown"/>
+  <pageSetup orientation="portrait" scale="100" pageOrder="overThenDown" blackAndWhite="0"/>
+  <headerFooter scaleWithDoc="1" alignWithMargins="1">
+    <oddHeader/>
+    <oddFooter/>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>